--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5982,7 +5982,7 @@
       </c>
       <c r="P73" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
+++ b/Tratamento/src/Dados_Limpos/novos/limpo_petz_20251130_201455.xlsx
@@ -4532,7 +4532,7 @@
       </c>
       <c r="P54" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -4922,7 +4922,7 @@
       </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5156,7 +5156,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7386,7 +7386,7 @@
       </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7462,7 +7462,7 @@
       </c>
       <c r="P93" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7538,7 +7538,7 @@
       </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
